--- a/docs/data/beidan_26084_dashboard.xlsx
+++ b/docs/data/beidan_26084_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26084期 比赛看板（皇冠历史相同亚盘） — 2026-08-11</t>
+          <t>⚽ 北京单场26084期 比赛看板（皇冠历史相同亚盘） — 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>2:0</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1432,20 +1484,24 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>球半</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>54%</t>
         </is>
       </c>
     </row>
@@ -1484,20 +1540,24 @@
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>29%</t>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>36%</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26084_dashboard.xlsx
+++ b/docs/data/beidan_26084_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26084期 比赛看板（皇冠历史相同亚盘） — 2026-08-12</t>
+          <t>⚽ 北京单场26084期 比赛看板（皇冠历史相同亚盘） — 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1424,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1480,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -1536,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1592,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1648,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1704,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
